--- a/data/trans_bre/IP16A10-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A10-Clase-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 21,2</t>
+          <t>-3,38; 20,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,14</t>
+          <t>0,0; 10,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,58</t>
+          <t>0,0; 19,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 6,0</t>
+          <t>-14,64; 6,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 34,49</t>
+          <t>-0,17; 34,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,33</t>
+          <t>0,0; 16,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 6,85</t>
+          <t>-3,99; 6,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 8,2</t>
+          <t>-0,88; 8,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 4,19</t>
+          <t>-4,49; 4,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,42</t>
+          <t>0,0; 20,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,27; 0,0</t>
+          <t>-15,07; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,49; 0,0</t>
+          <t>-31,44; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,57; 0,0</t>
+          <t>-27,24; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1114,27 +1114,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 8,35</t>
+          <t>0,72; 8,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 2,35</t>
+          <t>-2,19; 2,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 1,37</t>
+          <t>-2,98; 1,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 1029,66</t>
+          <t>-1,84; 1103,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-81,02; 326,7</t>
+          <t>-78,01; 412,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A10-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A10-Clase-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 20,81</t>
+          <t>-3,37; 20,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,19</t>
+          <t>0,0; 11,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,49</t>
+          <t>0,0; 19,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 6,03</t>
+          <t>-14,92; 6,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 34,61</t>
+          <t>-1,3; 37,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,41</t>
+          <t>0,0; 18,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 6,83</t>
+          <t>-3,93; 6,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 8,34</t>
+          <t>-0,89; 7,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 4,06</t>
+          <t>-4,86; 4,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,64</t>
+          <t>0,0; 17,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 0,0</t>
+          <t>-17,33; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,44; 0,0</t>
+          <t>-29,63; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 0,0</t>
+          <t>-26,31; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1114,27 +1114,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 8,48</t>
+          <t>0,66; 8,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 2,35</t>
+          <t>-2,54; 2,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 1,44</t>
+          <t>-2,61; 1,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1103,96</t>
+          <t>-10,92; 1129,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-78,01; 412,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A10-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A10-Clase-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea</t>
+          <t>Menores que consumieron  medicamentos para la diarrea</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 20,5</t>
+          <t>-3,24; 21,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,51</t>
+          <t>0,0; 12,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,63</t>
+          <t>0,0; 19,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,92; 6,29</t>
+          <t>-14,98; 6,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 37,28</t>
+          <t>-0,96; 34,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,82</t>
+          <t>0,0; 17,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 6,83</t>
+          <t>-3,88; 6,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 7,96</t>
+          <t>-0,87; 8,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 4,13</t>
+          <t>-4,09; 4,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,29</t>
+          <t>0,0; 19,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,33; 0,0</t>
+          <t>-14,27; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,63; 0,0</t>
+          <t>-29,49; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-26,31; 0,0</t>
+          <t>-30,57; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1114,27 +1114,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 8,21</t>
+          <t>0,55; 8,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 2,23</t>
+          <t>-2,29; 2,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1,46</t>
+          <t>-2,7; 1,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 1129,84</t>
+          <t>-15,09; 1029,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-81,02; 326,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A10-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A10-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,131 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>6,62</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,41</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>207,19%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.7236408920699575</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.7175061278483522</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1.029870743101171</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,24; 21,2</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 12,14</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-1.397964076854078</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.750454674778146</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.489913979174196</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>6,35</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-3,07</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-50,23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 19,58</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-14,98; 6,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.410890772704252</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.6284371837487135</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="n">
+        <v>-0.520016637235491</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>12,85</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,93</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>423,12%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="n">
+        <v>-3.603312349715253</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-0,96; 34,49</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 17,33</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5.182068559499537</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="n">
+        <v>0.5906426368151828</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,239 +735,135 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,49</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,44</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>79,73%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>269,96%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>24,8%</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n">
+        <v>1.947914048433727</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.7320361630482936</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>2.902234228493695</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,88; 6,85</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-0,87; 8,2</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-4,09; 4,19</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.5299980509410324</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>6.459176906485277</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.684576074552766</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>5,54</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-4,58</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 19,42</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-14,27; 0,0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>0.2720020862728822</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.6951745896465313</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1819228428195569</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.7578230570435723</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>2.423772395011226</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.5482308433028866</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-5,66</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-8,65</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.8056486583623707</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.2880167531116444</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.7481338581124567</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-29,49; 0,0</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-30,57; 0,0</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.28000459711464</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.540682360465795</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.189516525959621</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,77 +871,205 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>4,18</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>208,14%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-4,28%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-23,3%</t>
-        </is>
-      </c>
+      <c r="C16" s="5" t="n">
+        <v>1.002374767297435</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-1.096445261037994</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>0,55; 8,35</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-2,29; 2,35</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-2,7; 1,37</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-15,09; 1029,66</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-81,02; 326,7</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.473725107771029</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>3.46908597085721</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-0.8869705731980568</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-1.709434977256435</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-4.447574272962744</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-6.131593338486834</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.6666245288479721</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.003626138764584782</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.028186652592798</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>1.678156922874044</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.007514911637317701</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.09700762742567035</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0.03257139613607932</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.6164143190611641</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.4957186299610112</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-0.137620054869244</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.8246560020051328</v>
+      </c>
+      <c r="H23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1.399603096110745</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.6608755710023512</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.3589078361803299</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>10.6588098701477</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>4.017870386759794</v>
+      </c>
+      <c r="H24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1153,15 +1078,15 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
